--- a/artfynd/A 6784-2022 artfynd.xlsx
+++ b/artfynd/A 6784-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 6784-2022 artfynd.xlsx
+++ b/artfynd/A 6784-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -917,6 +917,130 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>125244593</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57469</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>102117</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Jorduggla</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Asio flammeus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Pontoppidan, 1763)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Långbodåsen, Långbodåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>442887</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6969621</v>
+      </c>
+      <c r="S4" t="n">
+        <v>50</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Oviken</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-05-19</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>21:51</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-05-19</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>21:51</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Beatrice Berg</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Beatrice Berg, Michael Englevid</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 6784-2022 artfynd.xlsx
+++ b/artfynd/A 6784-2022 artfynd.xlsx
@@ -922,7 +922,7 @@
         <v>125244593</v>
       </c>
       <c r="B4" t="n">
-        <v>57469</v>
+        <v>57486</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 6784-2022 artfynd.xlsx
+++ b/artfynd/A 6784-2022 artfynd.xlsx
@@ -922,7 +922,7 @@
         <v>125244593</v>
       </c>
       <c r="B4" t="n">
-        <v>57499</v>
+        <v>57500</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 6784-2022 artfynd.xlsx
+++ b/artfynd/A 6784-2022 artfynd.xlsx
@@ -922,7 +922,7 @@
         <v>125244593</v>
       </c>
       <c r="B4" t="n">
-        <v>57500</v>
+        <v>57504</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 6784-2022 artfynd.xlsx
+++ b/artfynd/A 6784-2022 artfynd.xlsx
@@ -922,7 +922,7 @@
         <v>125244593</v>
       </c>
       <c r="B4" t="n">
-        <v>57504</v>
+        <v>57505</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 6784-2022 artfynd.xlsx
+++ b/artfynd/A 6784-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,57 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>95057086</v>
+        <v>7070378</v>
       </c>
       <c r="B2" t="n">
-        <v>99611</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83304</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221343</v>
+        <v>311</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Brunklöver</t>
+          <t>Brun nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Trifolium spadiceum</t>
+          <t>Chaenotheca phaeocephala</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Turner) Th.Fr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Fäbodvägen, Jmt</t>
+          <t>Svedjebodarna, Fäbodvägen, ca 41 km SV om Ovikens k:a, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>440521.8058098741</v>
+        <v>441624</v>
       </c>
       <c r="R2" t="n">
-        <v>6968464.91667163</v>
+        <v>6969130</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-07-16</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2013-08-30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-07-16</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2013-08-30</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -773,39 +754,42 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Vägkant</t>
+          <t>timmerladan står på öppen mark i fäbodmiljö</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>rikligt på ved på nordöstra väggen av timmerbyggnad</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Janne Kolehmainen</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Janne Kolehmainen</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Ulrika Nordin, Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Hotade lavar på kulturved</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>95057093</v>
+        <v>119129392</v>
       </c>
       <c r="B3" t="n">
-        <v>96336</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83304</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -813,38 +797,41 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219811</v>
+        <v>311</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Brun nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Chaenotheca phaeocephala</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Turner) Th.Fr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Fäbodvägen, Jmt</t>
+          <t>Svedjebodarna, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>440521.8058098741</v>
+        <v>441624</v>
       </c>
       <c r="R3" t="n">
-        <v>6968464.91667163</v>
+        <v>6969123</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,22 +858,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-07-16</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-07-14</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-07-16</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-07-14</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,30 +876,30 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Vägkant</t>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>gammal fäbod</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Janne Kolehmainen</t>
+          <t>Johan Lorentzon</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Janne Kolehmainen</t>
+          <t>Johan Lorentzon</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125244593</v>
+        <v>7070377</v>
       </c>
       <c r="B4" t="n">
-        <v>57505</v>
+        <v>78685</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -930,49 +907,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102117</v>
+        <v>6443</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Jorduggla</t>
+          <t>Sotlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Asio flammeus</t>
+          <t>Acolium inquinans</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Pontoppidan, 1763)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
+          <t>(Sm.) A.Massal.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Långbodåsen, Långbodåsen, Jmt</t>
+          <t>Svedjebodarna, Fäbodvägen, ca 41 km SV om Ovikens k:a, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>442887</v>
+        <v>441624</v>
       </c>
       <c r="R4" t="n">
-        <v>6969621</v>
+        <v>6969130</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -996,22 +961,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>21:51</t>
+          <t>2013-08-30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>21:51</t>
+          <t>2013-08-30</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1022,19 +977,595 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>timmerladan står på öppen mark i fäbodmiljö</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>på ved på nordöstra väggen av timmerbyggnad</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Ulrika Nordin, Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Hotade lavar på kulturved</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>119129396</v>
+      </c>
+      <c r="B5" t="n">
+        <v>78685</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6443</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Sotlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Acolium inquinans</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Sm.) A.Massal.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Svedjebodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>441624</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6969123</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Oviken</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-07-14</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-07-14</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>gammal fäbod</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Johan Lorentzon</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Johan Lorentzon</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>125210716</v>
+      </c>
+      <c r="B6" t="n">
+        <v>56522</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>206004</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Skogshare</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lepus timidus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Svedjebodarna, Svedjebodarna, Oviken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>441537</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6969106</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Oviken</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-05-17</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-05-17</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Daniel Hedenbo</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Daniel Hedenbo</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>95057093</v>
+      </c>
+      <c r="B7" t="n">
+        <v>99120</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Fäbodvägen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>440522</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6968464</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Oviken</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2021-07-16</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2021-07-16</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Janne Kolehmainen</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Janne Kolehmainen</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>95057086</v>
+      </c>
+      <c r="B8" t="n">
+        <v>102464</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>221343</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Brunklöver</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Trifolium spadiceum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Fäbodvägen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>440522</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6968464</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Oviken</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2021-07-16</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2021-07-16</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Janne Kolehmainen</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Janne Kolehmainen</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>125244593</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57800</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>102117</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Jorduggla</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Asio flammeus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Pontoppidan, 1763)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Långbodåsen, Långbodåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>442887</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6969621</v>
+      </c>
+      <c r="S9" t="n">
+        <v>50</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Oviken</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-05-19</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>21:51</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-05-19</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>21:51</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
           <t>Beatrice Englevid</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
+      <c r="AX9" t="inlineStr">
         <is>
           <t>Beatrice Englevid, Michael Englevid</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr"/>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 6784-2022 artfynd.xlsx
+++ b/artfynd/A 6784-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
           <t>Hotade lavar på kulturved</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7070378</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -893,6 +903,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119129392</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1004,6 +1019,11 @@
           <t>Hotade lavar på kulturved</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7070377</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1114,6 +1134,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119129396</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1233,6 +1258,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125210716</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1340,6 +1370,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95057093</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1447,6 +1482,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95057086</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1566,8 +1606,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125244593</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>